--- a/production-test/files/Покупатели ежедневные.xlsx
+++ b/production-test/files/Покупатели ежедневные.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="394" documentId="8_{9C042B69-8A8F-4025-A362-7F9074BAFE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D920B733-F323-4655-9DDF-767B5EB35FF7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4E8073-0E2C-4F5C-BC70-ABB5406CE52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="БелторгФ" sheetId="7" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Яндекс.Л" sheetId="9" r:id="rId10"/>
     <sheet name="чл" sheetId="10" r:id="rId11"/>
     <sheet name="Экобиотехн" sheetId="11" r:id="rId12"/>
-    <sheet name="ЭЛЕМЕНТ-ТРЕЙД " sheetId="14" r:id="rId13"/>
+    <sheet name="ЭЛЕМЕНТ-ТРЕЙД" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -9194,7 +9194,7 @@
       <c r="C3" s="67"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="e">
-        <f>E2+B3-D3</f>
+        <f t="shared" ref="E3:E34" si="0">E2+B3-D3</f>
         <v>#REF!</v>
       </c>
       <c r="F3" s="160"/>
@@ -9217,7 +9217,7 @@
       <c r="C4" s="67"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="e">
-        <f>E3+B4-D4</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F4" s="160"/>
@@ -9225,7 +9225,7 @@
       <c r="H4" s="45"/>
       <c r="I4" s="45"/>
       <c r="J4" s="45">
-        <f t="shared" ref="J4:J70" si="0">J3+H4-I4</f>
+        <f t="shared" ref="J4:J70" si="1">J3+H4-I4</f>
         <v>0</v>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       <c r="C5" s="68"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7" t="e">
-        <f>E4+B5-D5</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F5" s="160"/>
@@ -9246,7 +9246,7 @@
       <c r="H5" s="45"/>
       <c r="I5" s="45"/>
       <c r="J5" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       <c r="C6" s="170"/>
       <c r="D6" s="171"/>
       <c r="E6" s="171" t="e">
-        <f>E5+B6-D6</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F6" s="160"/>
@@ -9269,7 +9269,7 @@
       <c r="H6" s="45"/>
       <c r="I6" s="45"/>
       <c r="J6" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
         <v>1897056</v>
       </c>
       <c r="E7" s="75" t="e">
-        <f>E6+B7-D7</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F7" s="175">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="I7" s="45"/>
       <c r="J7" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-54635.212800000001</v>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="7"/>
       <c r="E8" s="77" t="e">
-        <f>E7+B8-D8</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F8" s="175"/>
@@ -9324,7 +9324,7 @@
       <c r="H8" s="45"/>
       <c r="I8" s="45"/>
       <c r="J8" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-54635.212800000001</v>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       <c r="C9" s="28"/>
       <c r="D9" s="27"/>
       <c r="E9" s="79" t="e">
-        <f>E8+B9-D9</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F9" s="175"/>
@@ -9345,7 +9345,7 @@
       <c r="H9" s="45"/>
       <c r="I9" s="45"/>
       <c r="J9" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-54635.212800000001</v>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
         <v>2384870.3999999999</v>
       </c>
       <c r="E10" s="75" t="e">
-        <f>E9+B10-D10</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F10" s="175">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="I10" s="45"/>
       <c r="J10" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-123319.48032</v>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
         <v>1128960</v>
       </c>
       <c r="E11" s="77" t="e">
-        <f>E10+B11-D11</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F11" s="175">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="I11" s="45"/>
       <c r="J11" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-155833.52832000001</v>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="7"/>
       <c r="E12" s="77" t="e">
-        <f>E11+B12-D12</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F12" s="175"/>
@@ -9434,7 +9434,7 @@
       <c r="H12" s="45"/>
       <c r="I12" s="45"/>
       <c r="J12" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-155833.52832000001</v>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="7"/>
       <c r="E13" s="77" t="e">
-        <f>E12+B13-D13</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F13" s="175"/>
@@ -9455,7 +9455,7 @@
       <c r="H13" s="45"/>
       <c r="I13" s="45"/>
       <c r="J13" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-155833.52832000001</v>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       <c r="C14" s="28"/>
       <c r="D14" s="27"/>
       <c r="E14" s="79" t="e">
-        <f>E13+B14-D14</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F14" s="175"/>
@@ -9476,7 +9476,7 @@
       <c r="H14" s="45"/>
       <c r="I14" s="45"/>
       <c r="J14" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-155833.52832000001</v>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       <c r="C15" s="73"/>
       <c r="D15" s="159"/>
       <c r="E15" s="75" t="e">
-        <f>E14+B15-D15</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F15" s="175"/>
@@ -9499,7 +9499,7 @@
       <c r="H15" s="45"/>
       <c r="I15" s="45"/>
       <c r="J15" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-155833.52832000001</v>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       <c r="H16" s="45"/>
       <c r="I16" s="45"/>
       <c r="J16" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-155833.52832000001</v>
       </c>
     </row>
@@ -9535,7 +9535,7 @@
       <c r="C17" s="22"/>
       <c r="D17" s="24"/>
       <c r="E17" s="138" t="e">
-        <f>E16+B17-D17</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F17" s="175"/>
@@ -9543,7 +9543,7 @@
       <c r="H17" s="45"/>
       <c r="I17" s="45"/>
       <c r="J17" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-155833.52832000001</v>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
         <v>271008</v>
       </c>
       <c r="E18" s="138" t="e">
-        <f>E17+B18-D18</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F18" s="175">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="I18" s="45"/>
       <c r="J18" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-163638.55872</v>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
         <v>1762560</v>
       </c>
       <c r="E19" s="138" t="e">
-        <f>E18+B19-D19</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F19" s="175">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="I19" s="45"/>
       <c r="J19" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-214400.28672</v>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       <c r="C20" s="4"/>
       <c r="D20" s="7"/>
       <c r="E20" s="138" t="e">
-        <f>E19+B20-D20</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F20" s="175"/>
@@ -9634,7 +9634,7 @@
       <c r="H20" s="45"/>
       <c r="I20" s="45"/>
       <c r="J20" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-214400.28672</v>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="7"/>
       <c r="E21" s="138" t="e">
-        <f>E20+B21-D21</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F21" s="175"/>
@@ -9655,7 +9655,7 @@
       <c r="H21" s="45"/>
       <c r="I21" s="45"/>
       <c r="J21" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-214400.28672</v>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       <c r="C22" s="4"/>
       <c r="D22" s="7"/>
       <c r="E22" s="138" t="e">
-        <f>E21+B22-D22</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F22" s="175"/>
@@ -9676,7 +9676,7 @@
       <c r="H22" s="45"/>
       <c r="I22" s="45"/>
       <c r="J22" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-214400.28672</v>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
         <v>858528</v>
       </c>
       <c r="E23" s="185" t="e">
-        <f>E22+B23-D23</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F23" s="175">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="I23" s="45"/>
       <c r="J23" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       <c r="C24" s="212"/>
       <c r="D24" s="213"/>
       <c r="E24" s="224" t="e">
-        <f>E23+B24-D24</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F24" s="160"/>
@@ -9731,7 +9731,7 @@
       <c r="H24" s="45"/>
       <c r="I24" s="45"/>
       <c r="J24" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9745,7 +9745,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7" t="e">
-        <f>E24+B25-D25</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F25" s="160"/>
@@ -9753,7 +9753,7 @@
       <c r="H25" s="45"/>
       <c r="I25" s="45"/>
       <c r="J25" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
         <v>1596384</v>
       </c>
       <c r="E26" s="7" t="e">
-        <f>E25+B26-D26</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F26" s="160"/>
@@ -9779,7 +9779,7 @@
       <c r="H26" s="45"/>
       <c r="I26" s="45"/>
       <c r="J26" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9791,7 +9791,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7" t="e">
-        <f>E26+B27-D27</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F27" s="160"/>
@@ -9799,7 +9799,7 @@
       <c r="H27" s="45"/>
       <c r="I27" s="45"/>
       <c r="J27" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       <c r="H28" s="45"/>
       <c r="I28" s="45"/>
       <c r="J28" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7" t="e">
-        <f>E28+B29-D29</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F29" s="160"/>
@@ -9843,7 +9843,7 @@
       <c r="H29" s="45"/>
       <c r="I29" s="45"/>
       <c r="J29" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9853,7 +9853,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7" t="e">
-        <f>E29+B30-D30</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F30" s="160"/>
@@ -9861,7 +9861,7 @@
       <c r="H30" s="45"/>
       <c r="I30" s="45"/>
       <c r="J30" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="e">
-        <f>E30+B31-D31</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F31" s="160"/>
@@ -9879,7 +9879,7 @@
       <c r="H31" s="45"/>
       <c r="I31" s="45"/>
       <c r="J31" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       <c r="C32" s="4"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7" t="e">
-        <f>E31+B32-D32</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F32" s="160"/>
@@ -9897,7 +9897,7 @@
       <c r="H32" s="45"/>
       <c r="I32" s="45"/>
       <c r="J32" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9907,7 +9907,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7" t="e">
-        <f>E32+B33-D33</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F33" s="160"/>
@@ -9915,7 +9915,7 @@
       <c r="H33" s="45"/>
       <c r="I33" s="45"/>
       <c r="J33" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9925,7 +9925,7 @@
       <c r="C34" s="4"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7" t="e">
-        <f>E33+B34-D34</f>
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
       <c r="F34" s="160"/>
@@ -9933,7 +9933,7 @@
       <c r="H34" s="45"/>
       <c r="I34" s="45"/>
       <c r="J34" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7" t="e">
-        <f>E34+B35-D35</f>
+        <f t="shared" ref="E35:E66" si="2">E34+B35-D35</f>
         <v>#REF!</v>
       </c>
       <c r="F35" s="160"/>
@@ -9951,7 +9951,7 @@
       <c r="H35" s="45"/>
       <c r="I35" s="45"/>
       <c r="J35" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       <c r="C36" s="4"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7" t="e">
-        <f>E35+B36-D36</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F36" s="160"/>
@@ -9971,7 +9971,7 @@
       <c r="H36" s="45"/>
       <c r="I36" s="45"/>
       <c r="J36" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7" t="e">
-        <f>E36+B37-D37</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F37" s="160"/>
@@ -9991,7 +9991,7 @@
       <c r="H37" s="45"/>
       <c r="I37" s="45"/>
       <c r="J37" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       <c r="C38" s="4"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7" t="e">
-        <f>E37+B38-D38</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F38" s="160"/>
@@ -10009,7 +10009,7 @@
       <c r="H38" s="45"/>
       <c r="I38" s="45"/>
       <c r="J38" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       <c r="H39" s="45"/>
       <c r="I39" s="45"/>
       <c r="J39" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10051,7 +10051,7 @@
       <c r="H40" s="45"/>
       <c r="I40" s="45"/>
       <c r="J40" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       <c r="H41" s="45"/>
       <c r="I41" s="45"/>
       <c r="J41" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       <c r="C42" s="4"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7" t="e">
-        <f>E41+B42-D42</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F42" s="160"/>
@@ -10087,7 +10087,7 @@
       <c r="H42" s="45"/>
       <c r="I42" s="45"/>
       <c r="J42" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7" t="e">
-        <f>E42+B43-D43</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F43" s="160"/>
@@ -10105,7 +10105,7 @@
       <c r="H43" s="45"/>
       <c r="I43" s="45"/>
       <c r="J43" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       <c r="C44" s="4"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7" t="e">
-        <f>E43+B44-D44</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F44" s="160"/>
@@ -10123,7 +10123,7 @@
       <c r="H44" s="45"/>
       <c r="I44" s="45"/>
       <c r="J44" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7" t="e">
-        <f>E44+B45-D45</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F45" s="160"/>
@@ -10141,7 +10141,7 @@
       <c r="H45" s="45"/>
       <c r="I45" s="45"/>
       <c r="J45" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       <c r="C46" s="4"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7" t="e">
-        <f>E45+B46-D46</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F46" s="160"/>
@@ -10159,7 +10159,7 @@
       <c r="H46" s="45"/>
       <c r="I46" s="45"/>
       <c r="J46" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="e">
-        <f>E46+B47-D47</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F47" s="160"/>
@@ -10177,7 +10177,7 @@
       <c r="H47" s="45"/>
       <c r="I47" s="45"/>
       <c r="J47" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7" t="e">
-        <f>E47+B48-D48</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F48" s="160"/>
@@ -10195,7 +10195,7 @@
       <c r="H48" s="45"/>
       <c r="I48" s="45"/>
       <c r="J48" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7" t="e">
-        <f>E48+B49-D49</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F49" s="160"/>
@@ -10213,7 +10213,7 @@
       <c r="H49" s="45"/>
       <c r="I49" s="45"/>
       <c r="J49" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       <c r="C50" s="4"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7" t="e">
-        <f>E49+B50-D50</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F50" s="160"/>
@@ -10231,7 +10231,7 @@
       <c r="H50" s="45"/>
       <c r="I50" s="45"/>
       <c r="J50" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10241,7 +10241,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7" t="e">
-        <f>E50+B51-D51</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F51" s="160"/>
@@ -10249,7 +10249,7 @@
       <c r="H51" s="45"/>
       <c r="I51" s="45"/>
       <c r="J51" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       <c r="C52" s="4"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7" t="e">
-        <f>E51+B52-D52</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F52" s="160"/>
@@ -10267,7 +10267,7 @@
       <c r="H52" s="45"/>
       <c r="I52" s="45"/>
       <c r="J52" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       <c r="C53" s="9"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7" t="e">
-        <f>E52+B53-D53</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F53" s="160"/>
@@ -10285,7 +10285,7 @@
       <c r="H53" s="45"/>
       <c r="I53" s="45"/>
       <c r="J53" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10295,7 +10295,7 @@
       <c r="C54" s="4"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7" t="e">
-        <f>E53+B54-D54</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F54" s="160"/>
@@ -10303,7 +10303,7 @@
       <c r="H54" s="45"/>
       <c r="I54" s="45"/>
       <c r="J54" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10313,7 +10313,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7" t="e">
-        <f>E54+B55-D55</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F55" s="160"/>
@@ -10321,7 +10321,7 @@
       <c r="H55" s="45"/>
       <c r="I55" s="45"/>
       <c r="J55" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7" t="e">
-        <f>E55+B56-D56</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F56" s="160"/>
@@ -10339,7 +10339,7 @@
       <c r="H56" s="45"/>
       <c r="I56" s="45"/>
       <c r="J56" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       <c r="C57" s="4"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7" t="e">
-        <f>E56+B57-D57</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F57" s="160"/>
@@ -10357,7 +10357,7 @@
       <c r="H57" s="45"/>
       <c r="I57" s="45"/>
       <c r="J57" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10367,7 +10367,7 @@
       <c r="C58" s="4"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7" t="e">
-        <f>E57+B58-D58</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F58" s="160"/>
@@ -10375,7 +10375,7 @@
       <c r="H58" s="45"/>
       <c r="I58" s="45"/>
       <c r="J58" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10385,7 +10385,7 @@
       <c r="C59" s="4"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7" t="e">
-        <f>E58+B59-D59</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F59" s="160"/>
@@ -10393,7 +10393,7 @@
       <c r="H59" s="45"/>
       <c r="I59" s="45"/>
       <c r="J59" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10403,7 +10403,7 @@
       <c r="C60" s="9"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7" t="e">
-        <f>E59+B60-D60</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F60" s="160"/>
@@ -10411,7 +10411,7 @@
       <c r="H60" s="45"/>
       <c r="I60" s="45"/>
       <c r="J60" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10421,7 +10421,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7" t="e">
-        <f>E60+B61-D61</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F61" s="160"/>
@@ -10429,7 +10429,7 @@
       <c r="H61" s="45"/>
       <c r="I61" s="45"/>
       <c r="J61" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       <c r="C62" s="4"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7" t="e">
-        <f>E61+B62-D62</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F62" s="160"/>
@@ -10447,7 +10447,7 @@
       <c r="H62" s="45"/>
       <c r="I62" s="45"/>
       <c r="J62" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7" t="e">
-        <f>E62+B63-D63</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F63" s="160"/>
@@ -10465,7 +10465,7 @@
       <c r="H63" s="45"/>
       <c r="I63" s="45"/>
       <c r="J63" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
       <c r="C64" s="4"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7" t="e">
-        <f>E63+B64-D64</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F64" s="160"/>
@@ -10483,7 +10483,7 @@
       <c r="H64" s="45"/>
       <c r="I64" s="45"/>
       <c r="J64" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10493,7 +10493,7 @@
       <c r="C65" s="4"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7" t="e">
-        <f>E64+B65-D65</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F65" s="160"/>
@@ -10501,7 +10501,7 @@
       <c r="H65" s="45"/>
       <c r="I65" s="45"/>
       <c r="J65" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       <c r="C66" s="4"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7" t="e">
-        <f>E65+B66-D66</f>
+        <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="F66" s="160"/>
@@ -10519,7 +10519,7 @@
       <c r="H66" s="45"/>
       <c r="I66" s="45"/>
       <c r="J66" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
       <c r="C67" s="4"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7" t="e">
-        <f>E66+B67-D67</f>
+        <f t="shared" ref="E67:E73" si="3">E66+B67-D67</f>
         <v>#REF!</v>
       </c>
       <c r="F67" s="160"/>
@@ -10537,7 +10537,7 @@
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
       <c r="J67" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       <c r="C68" s="4"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7" t="e">
-        <f>E67+B68-D68</f>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
       <c r="F68" s="160"/>
@@ -10555,7 +10555,7 @@
       <c r="H68" s="45"/>
       <c r="I68" s="45"/>
       <c r="J68" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10565,7 +10565,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7" t="e">
-        <f>E68+B69-D69</f>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
       <c r="F69" s="160"/>
@@ -10573,7 +10573,7 @@
       <c r="H69" s="45"/>
       <c r="I69" s="45"/>
       <c r="J69" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7" t="e">
-        <f>E69+B70-D70</f>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
       <c r="F70" s="160"/>
@@ -10591,7 +10591,7 @@
       <c r="H70" s="45"/>
       <c r="I70" s="45"/>
       <c r="J70" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-239125.89311999999</v>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7" t="e">
-        <f>E70+B71-D71</f>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
       <c r="F71" s="160"/>
@@ -10619,7 +10619,7 @@
       <c r="C72" s="4"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7" t="e">
-        <f>E71+B72-D72</f>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
       <c r="F72" s="160"/>
@@ -10637,7 +10637,7 @@
       <c r="C73" s="4"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7" t="e">
-        <f>E72+B73-D73</f>
+        <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
       <c r="F73" s="160"/>
